--- a/config/union/union_fuben.xlsx
+++ b/config/union/union_fuben.xlsx
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B4" s="1" t="inlineStr">
         <is>
-          <t>ナツミ-制服</t>
+          <t>夏美-制服</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>ナツミ-制服が更に強力になった</t>
+          <t>纳兹米-制服变得更加强大</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>リコ-戦闘</t>
+          <t>里科-战斗</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>リコ-戦闘が更に強力になった</t>
+          <t>里科-战斗变得更加强大</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="B6" s="1" t="inlineStr">
         <is>
-          <t>モカ-騎士</t>
+          <t>摩卡骑士</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>モカ-騎士が更に強力になった</t>
+          <t>摩卡骑士变得更加强大</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>セイラ-魅惑</t>
+          <t>塞拉-魅惑</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>セイラ-魅惑が更に強力になった</t>
+          <t>塞拉-魔法变得更加强大</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>ユウリ-魅惑</t>
+          <t>有利-魅惑</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>ユウリ-魅惑が更に強力になった</t>
+          <t>尤利-魅惑变得更加强大</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>レオ-正装</t>
+          <t>莱奥-正装</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>レオ-正装が更に強力になった</t>
+          <t>雷欧-正装变得更加强大了</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>カリナ-水着</t>
+          <t>卡里娜-泳装</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>カリナ-水着が更に強力になった</t>
+          <t>卡莉娜-泳装变得更加强大</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>マコ-妖狐</t>
+          <t>魔狐-妖狐</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>マコ-妖狐が更に強力になった</t>
+          <t>魔狐变得更强大了</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ナツミ-制服</t>
+          <t>夏美-制服</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>ナツミ-制服が更に強力になった</t>
+          <t>纳兹米-制服变得更加强大</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>リコ-戦闘</t>
+          <t>里科-战斗</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>リコ-戦闘が更に強力になった</t>
+          <t>里科-战斗变得更加强大</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>モカ-騎士</t>
+          <t>摩卡骑士</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2034,7 +2034,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>モカ-騎士が更に強力になった</t>
+          <t>摩卡骑士变得更加强大</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>セイラ-魅惑</t>
+          <t>塞拉-魅惑</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>セイラ-魅惑が更に強力になった</t>
+          <t>塞拉-魔法变得更加强大</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ユウリ-魅惑</t>
+          <t>有利-魅惑</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>ユウリ-魅惑が更に強力になった</t>
+          <t>尤利-魅惑变得更加强大</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>レオ-正装</t>
+          <t>莱奥-正装</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>レオ-正装が更に強力になった</t>
+          <t>雷欧-正装变得更加强大了</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2269,7 +2269,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>カリナ-水着</t>
+          <t>卡里娜-泳装</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>カリナ-水着が更に強力になった</t>
+          <t>卡莉娜-泳装变得更加强大</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>マコ-妖狐</t>
+          <t>魔狐-妖狐</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>マコ-妖狐が更に強力になった</t>
+          <t>魔狐变得更强大了</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ナツミ-制服</t>
+          <t>夏美-制服</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>ナツミ-制服が更に強力になった</t>
+          <t>纳兹米-制服变得更加强大</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>リコ-戦闘</t>
+          <t>里科-战斗</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>リコ-戦闘が更に強力になった</t>
+          <t>里科-战斗变得更加强大</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2549,7 +2549,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>モカ-騎士</t>
+          <t>摩卡骑士</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2594,7 +2594,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>モカ-騎士が更に強力になった</t>
+          <t>摩卡骑士变得更加强大</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2619,7 +2619,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>セイラ-魅惑</t>
+          <t>塞拉-魅惑</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>セイラ-魅惑が更に強力になった</t>
+          <t>塞拉-魔法变得更加强大</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ユウリ-魅惑</t>
+          <t>有利-魅惑</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>ユウリ-魅惑が更に強力になった</t>
+          <t>尤利-魅惑变得更加强大</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>レオ-正装</t>
+          <t>莱奥-正装</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>レオ-正装が更に強力になった</t>
+          <t>雷欧-正装变得更加强大了</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>カリナ-水着</t>
+          <t>卡里娜-泳装</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>カリナ-水着が更に強力になった</t>
+          <t>卡莉娜-泳装变得更加强大</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>マコ-妖狐</t>
+          <t>魔狐-妖狐</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2944,7 +2944,7 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>マコ-妖狐が更に強力になった</t>
+          <t>魔狐变得更强大了</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ナツミ-制服</t>
+          <t>夏美-制服</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>ナツミ-制服が更に強力になった</t>
+          <t>纳兹米-制服变得更加强大</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>リコ-戦闘</t>
+          <t>里科-战斗</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>リコ-戦闘が更に強力になった</t>
+          <t>里科-战斗变得更加强大</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>モカ-騎士</t>
+          <t>摩卡骑士</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>モカ-騎士が更に強力になった</t>
+          <t>摩卡骑士变得更加强大</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3179,7 +3179,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>セイラ-魅惑</t>
+          <t>塞拉-魅惑</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>セイラ-魅惑が更に強力になった</t>
+          <t>塞拉-魔法变得更加强大</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ユウリ-魅惑</t>
+          <t>有利-魅惑</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>ユウリ-魅惑が更に強力になった</t>
+          <t>尤利-魅惑变得更加强大</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>レオ-正装</t>
+          <t>莱奥-正装</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>レオ-正装が更に強力になった</t>
+          <t>雷欧-正装变得更加强大了</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>カリナ-水着</t>
+          <t>卡里娜-泳装</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>カリナ-水着はもっと強い能力を獲得したようだ</t>
+          <t>卡莉娜-泳装似乎获得了更强的能力</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>マコ-妖狐</t>
+          <t>魔狐-妖狐</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>マコ-妖狐はもっと強い能力を獲得したようだ</t>
+          <t>魔狐似乎获得了更强的能力</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ナツミ-制服</t>
+          <t>夏美-制服</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>ナツミ-制服はもっと強い能力を獲得したようだ</t>
+          <t>纳兹米-制服似乎获得了更强的能力</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>リコ-戦闘</t>
+          <t>里科-战斗</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>リコ-戦闘はもっと強い能力を獲得したようだ</t>
+          <t>理光-战斗似乎获得了更强的能力</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>モカ-騎士</t>
+          <t>摩卡骑士</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3714,7 +3714,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>モカ-騎士はもっと強い能力を獲得したようだ</t>
+          <t>摩卡骑士似乎获得了更强的能力</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>セイラ-魅惑</t>
+          <t>塞拉-魅惑</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>セイラ-魅惑はもっと強い能力を獲得したようだ</t>
+          <t>塞拉-魔法似乎获得了更强的能力</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ユウリ-魅惑</t>
+          <t>有利-魅惑</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>ユウリ-魅惑はもっと強い能力を獲得したようだ</t>
+          <t>尤利-魅惑似乎获得了更强的能力</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>レオ-正装</t>
+          <t>莱奥-正装</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>レオ-正装はもっと強い能力を獲得したようだ</t>
+          <t>雷欧-正装似乎获得了更强的能力</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>カリナ-水着</t>
+          <t>卡里娜-泳装</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>カリナ-水着はもっと強い能力を獲得したようだ</t>
+          <t>卡莉娜-泳装似乎获得了更强的能力</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>マコ-妖狐</t>
+          <t>魔狐-妖狐</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4064,7 +4064,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>マコ-妖狐はもっと強い能力を獲得したようだ</t>
+          <t>魔狐似乎获得了更强的能力</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>マント 夏美</t>
+          <t>斗篷夏美</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>マント 夏美はもっと強い能力を獲得したようだ</t>
+          <t>斗篷夏美似乎获得了更强的能力</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>水着 夏美</t>
+          <t>泳装 夏美</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>水着 夏美はもっと強い能力を獲得したようだ</t>
+          <t>泳装夏美似乎获得了更强的能力</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>神尾 玲はもっと強い能力を獲得したようだ</t>
+          <t>神尾玲似乎获得了更强的能力</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>制服 神尾 玲はもっと強い能力を獲得したようだ</t>
+          <t>制服神尾玲似乎获得了更强的能力</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>真夏 咲</t>
+          <t>盛夏咲</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>真夏 咲はもっと強い能力を獲得したようだ</t>
+          <t>真夏咲似乎获得了更强的能力</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>千代はもっと強い能力を獲得したようだ</t>
+          <t>千代似乎获得了更强的能力</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>毒舌 千代はもっと強い能力を獲得したようだ</t>
+          <t>毒舌千代似乎获得了更强的能力</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>瑞希はもっと強い能力を獲得したようだ</t>
+          <t>瑞希好像获得了更强的能力</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>軽装 ルナ</t>
+          <t>不要轻装</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>軽装 ルナ はもっと強い能力を獲得したようだ</t>
+          <t>轻装露娜似乎获得了更强的能力</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>式典 リック</t>
+          <t>里克仪式</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4699,7 +4699,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>式典 リック はもっと強い能力を獲得したようだ</t>
+          <t>典礼里克似乎获得了更强的能力</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
